--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 7/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.08482</v>
+        <v>16.84842</v>
       </c>
       <c r="D2" t="n">
-        <v>16.48151</v>
+        <v>16.41861</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04781</v>
+        <v>16.84269</v>
       </c>
       <c r="F2" t="n">
-        <v>42.80434</v>
+        <v>43.33582</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05227</v>
+        <v>0.05043</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84354</v>
+        <v>1.87907</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.01831</v>
+        <v>17.30541</v>
       </c>
       <c r="D3" t="n">
-        <v>16.52009</v>
+        <v>16.77126</v>
       </c>
       <c r="E3" t="n">
-        <v>16.87904</v>
+        <v>16.81521</v>
       </c>
       <c r="F3" t="n">
-        <v>42.55961</v>
+        <v>42.21465</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05114</v>
+        <v>0.05056</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81981</v>
+        <v>1.83977</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.03723</v>
+        <v>17.06327</v>
       </c>
       <c r="D4" t="n">
-        <v>16.75015</v>
+        <v>16.75438</v>
       </c>
       <c r="E4" t="n">
-        <v>16.70866</v>
+        <v>16.99475</v>
       </c>
       <c r="F4" t="n">
-        <v>43.51945</v>
+        <v>43.64129</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05197</v>
+        <v>0.05053</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8253</v>
+        <v>1.87307</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.96081</v>
+        <v>16.77394</v>
       </c>
       <c r="D6" t="n">
-        <v>16.28473</v>
+        <v>16.13518</v>
       </c>
       <c r="E6" t="n">
-        <v>16.79956</v>
+        <v>16.60462</v>
       </c>
       <c r="F6" t="n">
-        <v>22.12075</v>
+        <v>21.81228</v>
       </c>
       <c r="G6" t="n">
-        <v>34.36146</v>
+        <v>34.39849</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.98854</v>
+        <v>16.85686</v>
       </c>
       <c r="D7" t="n">
-        <v>15.84374</v>
+        <v>16.3016</v>
       </c>
       <c r="E7" t="n">
-        <v>16.3986</v>
+        <v>16.67838</v>
       </c>
       <c r="F7" t="n">
-        <v>21.93389</v>
+        <v>22.46373</v>
       </c>
       <c r="G7" t="n">
-        <v>33.95097</v>
+        <v>34.8299</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.93313</v>
+        <v>16.89942</v>
       </c>
       <c r="D8" t="n">
-        <v>16.18183</v>
+        <v>16.15814</v>
       </c>
       <c r="E8" t="n">
-        <v>16.32898</v>
+        <v>16.60165</v>
       </c>
       <c r="F8" t="n">
-        <v>22.01711</v>
+        <v>21.64074</v>
       </c>
       <c r="G8" t="n">
-        <v>34.73174</v>
+        <v>34.29774</v>
       </c>
     </row>
   </sheetData>
